--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS06_resolution_sensitivity.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS06_resolution_sensitivity.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mean adjusted Rand index and normalized mutual information between the two halves of each donor split, over five seeds, at eight Leiden resolutions (0.5, 1, 2, 3, 5, 8, 12 and 20) for each cohort and region. The production resolution of 2.0 is flagged in `is_production`. The WGCNA rows carry no resolution, because there is none to set, and are kept so the sweep is read against the fixed baseline rather than against itself. Averaged across regions, agreement varies little over the whole sweep (mean ARI 0.37-0.47, production 0.42), and the best resolution differs by region (0.5, 0.5, 1, 3, 20 and 20), so no resolution is uniformly best and the production value is not a tuned optimum. Per-region production values span ARI 0.19-0.57 for IsoGraph against 0.29-0.71 for abundance WGCNA on the same splits, the same granularity contrast the funnel reports throughout.</t>
+          <t>Mean adjusted Rand index (ARI) and normalized mutual information between the two halves of each donor split, over five seeds, at eight Leiden resolutions (0.5, 1, 2, 3, 5, 8, 12, and 20) for each cohort and region. The production resolution of 2.0 is flagged in `is_production`. The weighted gene co-expression network analysis (WGCNA) rows carry no resolution, because there is none to set, and are kept so the sweep is read against the fixed baseline rather than against itself. Averaged across regions, agreement varies little over the whole sweep (mean ARI 0.37–0.47, production 0.42), and the best resolution differs by region (0.5, 0.5, 1, 3, 20 and 20), so no resolution is uniformly best and the production value is not a tuned optimum. Per-region production values span ARI 0.19–0.57 for IsoGraph against 0.29–0.71 for abundance WGCNA on the same splits, the same granularity contrast the funnel reports throughout.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30 by manuscript/_h/build_supplementary_data.py</t>
+          <t>2026-10-04 by manuscript/_h/build_supplementary_data.py</t>
         </is>
       </c>
     </row>
